--- a/Data/Home/Kitchen.COLevel.xlsx
+++ b/Data/Home/Kitchen.COLevel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709331980</v>
+        <v>1711876732</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709417633</v>
+        <v>1712129651</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1711077535</v>
+        <v>1712298464</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1711255609</v>
+        <v>1712535581</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1711516714</v>
+        <v>1712553249</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1711611305</v>
+        <v>1712622646</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,436 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1712792471</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1712902995</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1712907293</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1713085652</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1713113383</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1713335667</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1713432054</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1713586407</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1713601821</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1713681477</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1713946796</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1714276922</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COLevel_Change</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1714291639</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kitchen.COLevel.state: Acceptable</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
